--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_attendance.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_A1_attendance.xlsx
@@ -795,10 +795,10 @@
         <v>21</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>27</v>
@@ -810,7 +810,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" s="7" t="n">
         <v>27</v>
@@ -821,10 +821,8 @@
       <c r="R2" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S2" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T2" s="7" t="inlineStr">
         <is>
@@ -978,9 +976,9 @@
           <t>220302@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -997,10 +995,10 @@
         <v>20</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>27</v>
@@ -1012,7 +1010,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="7" t="n">
         <v>27</v>
@@ -1023,10 +1021,8 @@
       <c r="R3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S3" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T3" s="7" t="inlineStr">
         <is>
@@ -1199,10 +1195,10 @@
         <v>21</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>27</v>
@@ -1214,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" s="7" t="n">
         <v>27</v>
@@ -1225,10 +1221,8 @@
       <c r="R4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S4" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T4" s="7" t="inlineStr">
         <is>
@@ -1401,10 +1395,10 @@
         <v>21</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>27</v>
@@ -1416,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" s="7" t="n">
         <v>27</v>
@@ -1427,10 +1421,8 @@
       <c r="R5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S5" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
@@ -1584,9 +1576,9 @@
           <t>220307@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1603,10 +1595,10 @@
         <v>20</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>27</v>
@@ -1618,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="7" t="n">
         <v>27</v>
@@ -1629,10 +1621,8 @@
       <c r="R6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S6" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
@@ -1786,9 +1776,9 @@
           <t>220308@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1805,10 +1795,10 @@
         <v>20</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>27</v>
@@ -1820,7 +1810,7 @@
         <v>1</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="7" t="n">
         <v>27</v>
@@ -1831,10 +1821,8 @@
       <c r="R7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S7" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
@@ -1988,9 +1976,9 @@
           <t>220310@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2007,10 +1995,10 @@
         <v>20</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>27</v>
@@ -2022,7 +2010,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="7" t="n">
         <v>27</v>
@@ -2033,10 +2021,8 @@
       <c r="R8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S8" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T8" s="7" t="inlineStr">
         <is>
@@ -2209,10 +2195,10 @@
         <v>21</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>27</v>
@@ -2224,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" s="7" t="n">
         <v>27</v>
@@ -2235,10 +2221,8 @@
       <c r="R9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S9" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
@@ -2411,10 +2395,10 @@
         <v>21</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>27</v>
@@ -2426,7 +2410,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" s="7" t="n">
         <v>27</v>
@@ -2437,10 +2421,8 @@
       <c r="R10" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S10" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
@@ -2613,10 +2595,10 @@
         <v>21</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>27</v>
@@ -2628,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" s="7" t="n">
         <v>27</v>
@@ -2639,10 +2621,8 @@
       <c r="R11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S11" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
@@ -2815,10 +2795,10 @@
         <v>21</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>27</v>
@@ -2830,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12" s="7" t="n">
         <v>27</v>
@@ -2841,10 +2821,8 @@
       <c r="R12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S12" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T12" s="7" t="inlineStr">
         <is>
@@ -3017,10 +2995,10 @@
         <v>21</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>27</v>
@@ -3032,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P13" s="7" t="n">
         <v>27</v>
@@ -3043,10 +3021,8 @@
       <c r="R13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S13" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
@@ -3219,10 +3195,10 @@
         <v>21</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>27</v>
@@ -3234,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P14" s="7" t="n">
         <v>27</v>
@@ -3245,10 +3221,8 @@
       <c r="R14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S14" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T14" s="7" t="inlineStr">
         <is>
@@ -3402,9 +3376,9 @@
           <t>220320@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -3421,10 +3395,10 @@
         <v>20</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>27</v>
@@ -3436,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="7" t="n">
         <v>27</v>
@@ -3447,10 +3421,8 @@
       <c r="R15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S15" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T15" s="7" t="inlineStr">
         <is>
@@ -3604,9 +3576,9 @@
           <t>220323@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -3623,10 +3595,10 @@
         <v>20</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>27</v>
@@ -3638,7 +3610,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="7" t="n">
         <v>27</v>
@@ -3649,10 +3621,8 @@
       <c r="R16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S16" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T16" s="7" t="inlineStr">
         <is>
@@ -3806,9 +3776,9 @@
           <t>220324@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -3825,10 +3795,10 @@
         <v>20</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>27</v>
@@ -3840,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="7" t="n">
         <v>27</v>
@@ -3851,10 +3821,8 @@
       <c r="R17" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S17" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
@@ -4008,9 +3976,9 @@
           <t>220325@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -4027,10 +3995,10 @@
         <v>20</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>27</v>
@@ -4042,7 +4010,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="7" t="n">
         <v>27</v>
@@ -4053,10 +4021,8 @@
       <c r="R18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S18" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
@@ -4210,9 +4176,9 @@
           <t>220327@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -4229,10 +4195,10 @@
         <v>20</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>27</v>
@@ -4244,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="7" t="n">
         <v>27</v>
@@ -4255,10 +4221,8 @@
       <c r="R19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S19" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T19" s="7" t="inlineStr">
         <is>
@@ -4431,10 +4395,10 @@
         <v>21</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>27</v>
@@ -4446,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P20" s="7" t="n">
         <v>27</v>
@@ -4457,10 +4421,8 @@
       <c r="R20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S20" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
@@ -4633,10 +4595,10 @@
         <v>21</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>27</v>
@@ -4648,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" s="7" t="n">
         <v>27</v>
@@ -4659,10 +4621,8 @@
       <c r="R21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S21" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T21" s="7" t="inlineStr">
         <is>
@@ -4816,9 +4776,9 @@
           <t>220332@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -4835,10 +4795,10 @@
         <v>20</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>27</v>
@@ -4850,7 +4810,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="7" t="n">
         <v>27</v>
@@ -4861,10 +4821,8 @@
       <c r="R22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S22" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T22" s="7" t="inlineStr">
         <is>
@@ -5018,9 +4976,9 @@
           <t>220334@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -5037,10 +4995,10 @@
         <v>20</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>27</v>
@@ -5052,7 +5010,7 @@
         <v>1</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="7" t="n">
         <v>27</v>
@@ -5063,10 +5021,8 @@
       <c r="R23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S23" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
@@ -5220,9 +5176,9 @@
           <t>220335@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -5239,10 +5195,10 @@
         <v>20</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>27</v>
@@ -5254,7 +5210,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="7" t="n">
         <v>27</v>
@@ -5265,10 +5221,8 @@
       <c r="R24" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S24" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T24" s="7" t="inlineStr">
         <is>
@@ -5441,10 +5395,10 @@
         <v>21</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>27</v>
@@ -5456,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P25" s="7" t="n">
         <v>27</v>
@@ -5467,10 +5421,8 @@
       <c r="R25" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S25" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T25" s="7" t="inlineStr">
         <is>
@@ -5643,10 +5595,10 @@
         <v>21</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>27</v>
@@ -5658,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P26" s="7" t="n">
         <v>27</v>
@@ -5669,10 +5621,8 @@
       <c r="R26" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S26" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T26" s="7" t="inlineStr">
         <is>
@@ -5845,10 +5795,10 @@
         <v>21</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>27</v>
@@ -5860,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P27" s="7" t="n">
         <v>27</v>
@@ -5871,10 +5821,8 @@
       <c r="R27" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S27" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T27" s="7" t="inlineStr">
         <is>
@@ -6028,9 +5976,9 @@
           <t>220340@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -6047,10 +5995,10 @@
         <v>20</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>27</v>
@@ -6062,7 +6010,7 @@
         <v>1</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="7" t="n">
         <v>27</v>
@@ -6073,10 +6021,8 @@
       <c r="R28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S28" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T28" s="7" t="inlineStr">
         <is>
@@ -6249,10 +6195,10 @@
         <v>21</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>27</v>
@@ -6264,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P29" s="7" t="n">
         <v>27</v>
@@ -6275,10 +6221,8 @@
       <c r="R29" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S29" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T29" s="7" t="inlineStr">
         <is>
@@ -6432,9 +6376,9 @@
           <t>220342@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -6451,10 +6395,10 @@
         <v>20</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>27</v>
@@ -6466,7 +6410,7 @@
         <v>1</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="7" t="n">
         <v>27</v>
@@ -6477,10 +6421,8 @@
       <c r="R30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S30" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T30" s="7" t="inlineStr">
         <is>
@@ -6634,9 +6576,9 @@
           <t>220343@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -6653,10 +6595,10 @@
         <v>20</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>27</v>
@@ -6668,7 +6610,7 @@
         <v>1</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" s="7" t="n">
         <v>27</v>
@@ -6679,10 +6621,8 @@
       <c r="R31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S31" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T31" s="7" t="inlineStr">
         <is>
@@ -6855,10 +6795,10 @@
         <v>21</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>27</v>
@@ -6870,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" s="7" t="n">
         <v>27</v>
@@ -6881,10 +6821,8 @@
       <c r="R32" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S32" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T32" s="7" t="inlineStr">
         <is>
@@ -7038,9 +6976,9 @@
           <t>220346@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -7057,10 +6995,10 @@
         <v>20</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>27</v>
@@ -7072,7 +7010,7 @@
         <v>1</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" s="7" t="n">
         <v>27</v>
@@ -7083,10 +7021,8 @@
       <c r="R33" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S33" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
@@ -7259,10 +7195,10 @@
         <v>21</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>27</v>
@@ -7274,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34" s="7" t="n">
         <v>27</v>
@@ -7285,10 +7221,8 @@
       <c r="R34" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S34" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T34" s="7" t="inlineStr">
         <is>
@@ -7461,10 +7395,10 @@
         <v>21</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>27</v>
@@ -7476,7 +7410,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35" s="7" t="n">
         <v>27</v>
@@ -7487,10 +7421,8 @@
       <c r="R35" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S35" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T35" s="7" t="inlineStr">
         <is>
@@ -7644,9 +7576,9 @@
           <t>220349@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -7663,10 +7595,10 @@
         <v>20</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>27</v>
@@ -7678,7 +7610,7 @@
         <v>1</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" s="7" t="n">
         <v>27</v>
@@ -7689,10 +7621,8 @@
       <c r="R36" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S36" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T36" s="7" t="inlineStr">
         <is>
@@ -7846,9 +7776,9 @@
           <t>220350@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -7865,10 +7795,10 @@
         <v>20</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>27</v>
@@ -7880,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" s="7" t="n">
         <v>27</v>
@@ -7891,10 +7821,8 @@
       <c r="R37" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S37" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T37" s="7" t="inlineStr">
         <is>
@@ -8067,10 +7995,10 @@
         <v>21</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>27</v>
@@ -8082,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" s="7" t="n">
         <v>27</v>
@@ -8093,10 +8021,8 @@
       <c r="R38" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S38" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T38" s="7" t="inlineStr">
         <is>
@@ -8269,10 +8195,10 @@
         <v>21</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>27</v>
@@ -8284,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P39" s="7" t="n">
         <v>27</v>
@@ -8295,10 +8221,8 @@
       <c r="R39" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S39" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T39" s="7" t="inlineStr">
         <is>
@@ -8471,10 +8395,10 @@
         <v>21</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>27</v>
@@ -8486,7 +8410,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P40" s="7" t="n">
         <v>27</v>
@@ -8497,10 +8421,8 @@
       <c r="R40" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S40" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T40" s="7" t="inlineStr">
         <is>
@@ -8673,10 +8595,10 @@
         <v>21</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="6" t="n">
         <v>27</v>
@@ -8688,7 +8610,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P41" s="7" t="n">
         <v>27</v>
@@ -8699,10 +8621,8 @@
       <c r="R41" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S41" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T41" s="7" t="inlineStr">
         <is>
@@ -8856,9 +8776,9 @@
           <t>220355@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -8875,10 +8795,10 @@
         <v>20</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L42" s="6" t="n">
         <v>27</v>
@@ -8890,7 +8810,7 @@
         <v>1</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" s="7" t="n">
         <v>27</v>
@@ -8901,10 +8821,8 @@
       <c r="R42" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S42" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T42" s="7" t="inlineStr">
         <is>
@@ -9058,9 +8976,9 @@
           <t>220356@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -9077,10 +8995,10 @@
         <v>20</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" s="6" t="n">
         <v>27</v>
@@ -9092,7 +9010,7 @@
         <v>1</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" s="7" t="n">
         <v>27</v>
@@ -9103,10 +9021,8 @@
       <c r="R43" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S43" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T43" s="7" t="inlineStr">
         <is>
@@ -9260,9 +9176,9 @@
           <t>220357@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -9279,10 +9195,10 @@
         <v>20</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>27</v>
@@ -9294,7 +9210,7 @@
         <v>1</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" s="7" t="n">
         <v>27</v>
@@ -9305,10 +9221,8 @@
       <c r="R44" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S44" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T44" s="7" t="inlineStr">
         <is>
@@ -9462,9 +9376,9 @@
           <t>220358@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -9481,10 +9395,10 @@
         <v>20</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>27</v>
@@ -9496,7 +9410,7 @@
         <v>1</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" s="7" t="n">
         <v>27</v>
@@ -9507,10 +9421,8 @@
       <c r="R45" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S45" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T45" s="7" t="inlineStr">
         <is>
@@ -9664,9 +9576,9 @@
           <t>220359@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -9683,10 +9595,10 @@
         <v>20</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>27</v>
@@ -9698,7 +9610,7 @@
         <v>1</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" s="7" t="n">
         <v>27</v>
@@ -9709,10 +9621,8 @@
       <c r="R46" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S46" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T46" s="7" t="inlineStr">
         <is>
@@ -9866,9 +9776,9 @@
           <t>220360@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -9885,10 +9795,10 @@
         <v>20</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>27</v>
@@ -9900,7 +9810,7 @@
         <v>1</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" s="7" t="n">
         <v>27</v>
@@ -9911,10 +9821,8 @@
       <c r="R47" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S47" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T47" s="7" t="inlineStr">
         <is>
@@ -10068,9 +9976,9 @@
           <t>220361@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -10087,10 +9995,10 @@
         <v>20</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>27</v>
@@ -10102,7 +10010,7 @@
         <v>1</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48" s="7" t="n">
         <v>27</v>
@@ -10113,10 +10021,8 @@
       <c r="R48" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S48" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T48" s="7" t="inlineStr">
         <is>
@@ -10289,10 +10195,10 @@
         <v>21</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>27</v>
@@ -10304,7 +10210,7 @@
         <v>0</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P49" s="7" t="n">
         <v>27</v>
@@ -10315,10 +10221,8 @@
       <c r="R49" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S49" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T49" s="7" t="inlineStr">
         <is>
@@ -10472,9 +10376,9 @@
           <t>220363@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -10491,10 +10395,10 @@
         <v>20</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>27</v>
@@ -10506,7 +10410,7 @@
         <v>1</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="7" t="n">
         <v>27</v>
@@ -10517,10 +10421,8 @@
       <c r="R50" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S50" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T50" s="7" t="inlineStr">
         <is>
@@ -10693,10 +10595,10 @@
         <v>21</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" s="6" t="n">
         <v>27</v>
@@ -10708,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P51" s="7" t="n">
         <v>27</v>
@@ -10719,10 +10621,8 @@
       <c r="R51" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S51" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T51" s="7" t="inlineStr">
         <is>
@@ -10876,9 +10776,9 @@
           <t>220369@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -10895,10 +10795,10 @@
         <v>20</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>27</v>
@@ -10910,7 +10810,7 @@
         <v>1</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52" s="7" t="n">
         <v>27</v>
@@ -10921,10 +10821,8 @@
       <c r="R52" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S52" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T52" s="7" t="inlineStr">
         <is>
@@ -11078,9 +10976,9 @@
           <t>220371@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -11097,10 +10995,10 @@
         <v>20</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>27</v>
@@ -11112,7 +11010,7 @@
         <v>1</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" s="7" t="n">
         <v>27</v>
@@ -11123,10 +11021,8 @@
       <c r="R53" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S53" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T53" s="7" t="inlineStr">
         <is>
@@ -11280,9 +11176,9 @@
           <t>220373@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -11299,10 +11195,10 @@
         <v>20</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="6" t="n">
         <v>27</v>
@@ -11314,7 +11210,7 @@
         <v>1</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" s="7" t="n">
         <v>27</v>
@@ -11325,10 +11221,8 @@
       <c r="R54" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S54" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T54" s="7" t="inlineStr">
         <is>
@@ -11501,10 +11395,10 @@
         <v>21</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>27</v>
@@ -11516,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P55" s="7" t="n">
         <v>27</v>
@@ -11527,10 +11421,8 @@
       <c r="R55" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S55" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T55" s="7" t="inlineStr">
         <is>
@@ -11684,9 +11576,9 @@
           <t>220376@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -11703,10 +11595,10 @@
         <v>20</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56" s="6" t="n">
         <v>27</v>
@@ -11718,7 +11610,7 @@
         <v>1</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P56" s="7" t="n">
         <v>27</v>
@@ -11729,10 +11621,8 @@
       <c r="R56" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S56" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T56" s="7" t="inlineStr">
         <is>
@@ -11905,10 +11795,10 @@
         <v>21</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="6" t="n">
         <v>27</v>
@@ -11920,7 +11810,7 @@
         <v>0</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P57" s="7" t="n">
         <v>27</v>
@@ -11931,10 +11821,8 @@
       <c r="R57" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S57" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T57" s="7" t="inlineStr">
         <is>
@@ -12107,10 +11995,10 @@
         <v>21</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="6" t="n">
         <v>27</v>
@@ -12122,7 +12010,7 @@
         <v>0</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P58" s="7" t="n">
         <v>27</v>
@@ -12133,10 +12021,8 @@
       <c r="R58" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S58" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T58" s="7" t="inlineStr">
         <is>
@@ -12290,9 +12176,9 @@
           <t>220379@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -12309,10 +12195,10 @@
         <v>20</v>
       </c>
       <c r="J59" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>27</v>
@@ -12324,7 +12210,7 @@
         <v>1</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" s="7" t="n">
         <v>27</v>
@@ -12335,10 +12221,8 @@
       <c r="R59" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S59" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T59" s="7" t="inlineStr">
         <is>
@@ -12492,9 +12376,9 @@
           <t>220380@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -12511,10 +12395,10 @@
         <v>20</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" s="6" t="n">
         <v>27</v>
@@ -12526,7 +12410,7 @@
         <v>1</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P60" s="7" t="n">
         <v>27</v>
@@ -12537,10 +12421,8 @@
       <c r="R60" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S60" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T60" s="7" t="inlineStr">
         <is>
@@ -12713,10 +12595,10 @@
         <v>21</v>
       </c>
       <c r="J61" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L61" s="6" t="n">
         <v>27</v>
@@ -12728,7 +12610,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P61" s="7" t="n">
         <v>27</v>
@@ -12739,10 +12621,8 @@
       <c r="R61" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S61" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T61" s="7" t="inlineStr">
         <is>
@@ -12915,10 +12795,10 @@
         <v>21</v>
       </c>
       <c r="J62" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>27</v>
@@ -12930,7 +12810,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P62" s="7" t="n">
         <v>27</v>
@@ -12941,10 +12821,8 @@
       <c r="R62" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S62" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T62" s="7" t="inlineStr">
         <is>
@@ -13098,9 +12976,9 @@
           <t>220383@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -13117,10 +12995,10 @@
         <v>20</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="6" t="n">
         <v>27</v>
@@ -13132,7 +13010,7 @@
         <v>1</v>
       </c>
       <c r="O63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P63" s="7" t="n">
         <v>27</v>
@@ -13143,10 +13021,8 @@
       <c r="R63" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S63" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T63" s="7" t="inlineStr">
         <is>
@@ -13319,10 +13195,10 @@
         <v>21</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>27</v>
@@ -13334,7 +13210,7 @@
         <v>0</v>
       </c>
       <c r="O64" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P64" s="7" t="n">
         <v>27</v>
@@ -13345,10 +13221,8 @@
       <c r="R64" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S64" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T64" s="7" t="inlineStr">
         <is>
@@ -13502,9 +13376,9 @@
           <t>220385@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -13521,10 +13395,10 @@
         <v>20</v>
       </c>
       <c r="J65" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>27</v>
@@ -13536,7 +13410,7 @@
         <v>1</v>
       </c>
       <c r="O65" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P65" s="7" t="n">
         <v>27</v>
@@ -13547,10 +13421,8 @@
       <c r="R65" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S65" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T65" s="7" t="inlineStr">
         <is>
@@ -13704,9 +13576,9 @@
           <t>220386@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -13723,10 +13595,10 @@
         <v>20</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66" s="6" t="n">
         <v>27</v>
@@ -13738,7 +13610,7 @@
         <v>1</v>
       </c>
       <c r="O66" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" s="7" t="n">
         <v>27</v>
@@ -13749,10 +13621,8 @@
       <c r="R66" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S66" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S66" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T66" s="7" t="inlineStr">
         <is>
@@ -13925,10 +13795,10 @@
         <v>21</v>
       </c>
       <c r="J67" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>27</v>
@@ -13940,7 +13810,7 @@
         <v>0</v>
       </c>
       <c r="O67" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P67" s="7" t="n">
         <v>27</v>
@@ -13951,10 +13821,8 @@
       <c r="R67" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S67" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S67" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T67" s="7" t="inlineStr">
         <is>
@@ -14127,10 +13995,10 @@
         <v>21</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68" s="6" t="n">
         <v>27</v>
@@ -14142,7 +14010,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P68" s="7" t="n">
         <v>27</v>
@@ -14153,10 +14021,8 @@
       <c r="R68" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S68" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S68" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T68" s="7" t="inlineStr">
         <is>
@@ -14310,9 +14176,9 @@
           <t>220390@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F69" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -14329,10 +14195,10 @@
         <v>20</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>27</v>
@@ -14344,7 +14210,7 @@
         <v>1</v>
       </c>
       <c r="O69" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P69" s="7" t="n">
         <v>27</v>
@@ -14355,10 +14221,8 @@
       <c r="R69" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S69" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S69" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T69" s="7" t="inlineStr">
         <is>
@@ -14512,9 +14376,9 @@
           <t>220393@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -14531,10 +14395,10 @@
         <v>20</v>
       </c>
       <c r="J70" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" s="6" t="n">
         <v>27</v>
@@ -14546,7 +14410,7 @@
         <v>1</v>
       </c>
       <c r="O70" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P70" s="7" t="n">
         <v>27</v>
@@ -14557,10 +14421,8 @@
       <c r="R70" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S70" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T70" s="7" t="inlineStr">
         <is>
@@ -14714,9 +14576,9 @@
           <t>220394@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
@@ -14733,10 +14595,10 @@
         <v>20</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="6" t="n">
         <v>27</v>
@@ -14748,7 +14610,7 @@
         <v>1</v>
       </c>
       <c r="O71" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P71" s="7" t="n">
         <v>27</v>
@@ -14759,10 +14621,8 @@
       <c r="R71" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S71" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S71" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T71" s="7" t="inlineStr">
         <is>
@@ -14916,9 +14776,9 @@
           <t>220396@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -14935,10 +14795,10 @@
         <v>20</v>
       </c>
       <c r="J72" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>27</v>
@@ -14950,7 +14810,7 @@
         <v>1</v>
       </c>
       <c r="O72" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" s="7" t="n">
         <v>27</v>
@@ -14961,10 +14821,8 @@
       <c r="R72" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S72" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S72" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T72" s="7" t="inlineStr">
         <is>
@@ -15118,9 +14976,9 @@
           <t>220397@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -15137,10 +14995,10 @@
         <v>20</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>27</v>
@@ -15152,7 +15010,7 @@
         <v>1</v>
       </c>
       <c r="O73" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P73" s="7" t="n">
         <v>27</v>
@@ -15163,10 +15021,8 @@
       <c r="R73" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S73" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S73" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T73" s="7" t="inlineStr">
         <is>
@@ -15339,10 +15195,10 @@
         <v>21</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L74" s="6" t="n">
         <v>27</v>
@@ -15354,7 +15210,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P74" s="7" t="n">
         <v>27</v>
@@ -15365,10 +15221,8 @@
       <c r="R74" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S74" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S74" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T74" s="7" t="inlineStr">
         <is>
@@ -15522,9 +15376,9 @@
           <t>220399@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -15541,10 +15395,10 @@
         <v>20</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>27</v>
@@ -15556,7 +15410,7 @@
         <v>1</v>
       </c>
       <c r="O75" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75" s="7" t="n">
         <v>27</v>
@@ -15567,10 +15421,8 @@
       <c r="R75" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S75" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S75" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T75" s="7" t="inlineStr">
         <is>
@@ -15724,9 +15576,9 @@
           <t>220400@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -15743,10 +15595,10 @@
         <v>20</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>27</v>
@@ -15758,7 +15610,7 @@
         <v>1</v>
       </c>
       <c r="O76" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P76" s="7" t="n">
         <v>27</v>
@@ -15769,10 +15621,8 @@
       <c r="R76" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S76" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T76" s="7" t="inlineStr">
         <is>
@@ -15926,9 +15776,9 @@
           <t>220401@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
@@ -15945,10 +15795,10 @@
         <v>20</v>
       </c>
       <c r="J77" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" s="6" t="n">
         <v>27</v>
@@ -15960,7 +15810,7 @@
         <v>1</v>
       </c>
       <c r="O77" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P77" s="7" t="n">
         <v>27</v>
@@ -15971,10 +15821,8 @@
       <c r="R77" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S77" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S77" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T77" s="7" t="inlineStr">
         <is>
@@ -16128,9 +15976,9 @@
           <t>220402@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -16147,10 +15995,10 @@
         <v>20</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>27</v>
@@ -16162,7 +16010,7 @@
         <v>1</v>
       </c>
       <c r="O78" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P78" s="7" t="n">
         <v>27</v>
@@ -16173,10 +16021,8 @@
       <c r="R78" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S78" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S78" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T78" s="7" t="inlineStr">
         <is>
@@ -16330,9 +16176,9 @@
           <t>220403@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -16349,10 +16195,10 @@
         <v>20</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L79" s="6" t="n">
         <v>27</v>
@@ -16364,7 +16210,7 @@
         <v>1</v>
       </c>
       <c r="O79" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P79" s="7" t="n">
         <v>27</v>
@@ -16375,10 +16221,8 @@
       <c r="R79" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S79" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S79" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T79" s="7" t="inlineStr">
         <is>
@@ -16532,9 +16376,9 @@
           <t>220404@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -16551,10 +16395,10 @@
         <v>20</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>27</v>
@@ -16566,7 +16410,7 @@
         <v>1</v>
       </c>
       <c r="O80" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P80" s="7" t="n">
         <v>27</v>
@@ -16577,10 +16421,8 @@
       <c r="R80" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S80" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T80" s="7" t="inlineStr">
         <is>
@@ -16753,10 +16595,10 @@
         <v>21</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="6" t="n">
         <v>27</v>
@@ -16768,7 +16610,7 @@
         <v>0</v>
       </c>
       <c r="O81" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P81" s="7" t="n">
         <v>27</v>
@@ -16779,10 +16621,8 @@
       <c r="R81" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S81" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S81" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T81" s="7" t="inlineStr">
         <is>
@@ -16936,9 +16776,9 @@
           <t>220406@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -16955,10 +16795,10 @@
         <v>20</v>
       </c>
       <c r="J82" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>27</v>
@@ -16970,7 +16810,7 @@
         <v>1</v>
       </c>
       <c r="O82" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P82" s="7" t="n">
         <v>27</v>
@@ -16981,10 +16821,8 @@
       <c r="R82" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S82" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S82" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T82" s="7" t="inlineStr">
         <is>
@@ -17138,9 +16976,9 @@
           <t>220407@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
@@ -17157,10 +16995,10 @@
         <v>20</v>
       </c>
       <c r="J83" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>27</v>
@@ -17172,7 +17010,7 @@
         <v>1</v>
       </c>
       <c r="O83" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P83" s="7" t="n">
         <v>27</v>
@@ -17183,10 +17021,8 @@
       <c r="R83" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S83" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S83" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T83" s="7" t="inlineStr">
         <is>
@@ -17340,9 +17176,9 @@
           <t>220408@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -17359,10 +17195,10 @@
         <v>20</v>
       </c>
       <c r="J84" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>27</v>
@@ -17374,7 +17210,7 @@
         <v>1</v>
       </c>
       <c r="O84" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P84" s="7" t="n">
         <v>27</v>
@@ -17385,10 +17221,8 @@
       <c r="R84" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S84" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S84" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T84" s="7" t="inlineStr">
         <is>
@@ -17542,9 +17376,9 @@
           <t>220409@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -17561,10 +17395,10 @@
         <v>20</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" s="6" t="n">
         <v>27</v>
@@ -17576,7 +17410,7 @@
         <v>1</v>
       </c>
       <c r="O85" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" s="7" t="n">
         <v>27</v>
@@ -17587,10 +17421,8 @@
       <c r="R85" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S85" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S85" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T85" s="7" t="inlineStr">
         <is>
@@ -17744,9 +17576,9 @@
           <t>220410@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -17763,10 +17595,10 @@
         <v>20</v>
       </c>
       <c r="J86" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>27</v>
@@ -17778,7 +17610,7 @@
         <v>1</v>
       </c>
       <c r="O86" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" s="7" t="n">
         <v>27</v>
@@ -17789,10 +17621,8 @@
       <c r="R86" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S86" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T86" s="7" t="inlineStr">
         <is>
@@ -17965,10 +17795,10 @@
         <v>21</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="6" t="n">
         <v>27</v>
@@ -17980,7 +17810,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P87" s="7" t="n">
         <v>27</v>
@@ -17991,10 +17821,8 @@
       <c r="R87" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S87" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S87" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T87" s="7" t="inlineStr">
         <is>
@@ -18167,10 +17995,10 @@
         <v>21</v>
       </c>
       <c r="J88" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="6" t="n">
         <v>27</v>
@@ -18182,7 +18010,7 @@
         <v>0</v>
       </c>
       <c r="O88" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P88" s="7" t="n">
         <v>27</v>
@@ -18193,10 +18021,8 @@
       <c r="R88" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S88" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S88" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T88" s="7" t="inlineStr">
         <is>
@@ -18350,9 +18176,9 @@
           <t>220413@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
@@ -18369,10 +18195,10 @@
         <v>20</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>27</v>
@@ -18384,7 +18210,7 @@
         <v>1</v>
       </c>
       <c r="O89" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89" s="7" t="n">
         <v>27</v>
@@ -18395,10 +18221,8 @@
       <c r="R89" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S89" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S89" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T89" s="7" t="inlineStr">
         <is>
@@ -18552,9 +18376,9 @@
           <t>220415@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -18571,10 +18395,10 @@
         <v>20</v>
       </c>
       <c r="J90" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>27</v>
@@ -18586,7 +18410,7 @@
         <v>1</v>
       </c>
       <c r="O90" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P90" s="7" t="n">
         <v>27</v>
@@ -18597,10 +18421,8 @@
       <c r="R90" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S90" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S90" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T90" s="7" t="inlineStr">
         <is>
@@ -18754,9 +18576,9 @@
           <t>220416@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
@@ -18773,10 +18595,10 @@
         <v>20</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91" s="6" t="n">
         <v>27</v>
@@ -18788,7 +18610,7 @@
         <v>1</v>
       </c>
       <c r="O91" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P91" s="7" t="n">
         <v>27</v>
@@ -18799,10 +18621,8 @@
       <c r="R91" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S91" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T91" s="7" t="inlineStr">
         <is>
@@ -18956,9 +18776,9 @@
           <t>220417@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F92" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -18975,10 +18795,10 @@
         <v>20</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>27</v>
@@ -18990,7 +18810,7 @@
         <v>1</v>
       </c>
       <c r="O92" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P92" s="7" t="n">
         <v>27</v>
@@ -19001,10 +18821,8 @@
       <c r="R92" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S92" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S92" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T92" s="7" t="inlineStr">
         <is>
@@ -19158,9 +18976,9 @@
           <t>220418@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -19177,10 +18995,10 @@
         <v>20</v>
       </c>
       <c r="J93" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>27</v>
@@ -19192,7 +19010,7 @@
         <v>1</v>
       </c>
       <c r="O93" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P93" s="7" t="n">
         <v>27</v>
@@ -19203,10 +19021,8 @@
       <c r="R93" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S93" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S93" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T93" s="7" t="inlineStr">
         <is>
@@ -19360,9 +19176,9 @@
           <t>220419@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F94" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -19379,10 +19195,10 @@
         <v>20</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L94" s="6" t="n">
         <v>27</v>
@@ -19394,7 +19210,7 @@
         <v>1</v>
       </c>
       <c r="O94" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94" s="7" t="n">
         <v>27</v>
@@ -19405,10 +19221,8 @@
       <c r="R94" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S94" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S94" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T94" s="7" t="inlineStr">
         <is>
@@ -19562,9 +19376,9 @@
           <t>220420@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F95" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -19581,10 +19395,10 @@
         <v>20</v>
       </c>
       <c r="J95" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K95" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L95" s="6" t="n">
         <v>27</v>
@@ -19596,7 +19410,7 @@
         <v>1</v>
       </c>
       <c r="O95" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P95" s="7" t="n">
         <v>27</v>
@@ -19607,10 +19421,8 @@
       <c r="R95" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S95" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S95" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T95" s="7" t="inlineStr">
         <is>
@@ -19764,9 +19576,9 @@
           <t>220421@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -19783,10 +19595,10 @@
         <v>20</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L96" s="6" t="n">
         <v>27</v>
@@ -19798,7 +19610,7 @@
         <v>1</v>
       </c>
       <c r="O96" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" s="7" t="n">
         <v>27</v>
@@ -19809,10 +19621,8 @@
       <c r="R96" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S96" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S96" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T96" s="7" t="inlineStr">
         <is>
@@ -19966,9 +19776,9 @@
           <t>220422@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F97" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
@@ -19985,10 +19795,10 @@
         <v>20</v>
       </c>
       <c r="J97" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L97" s="6" t="n">
         <v>27</v>
@@ -20000,7 +19810,7 @@
         <v>1</v>
       </c>
       <c r="O97" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" s="7" t="n">
         <v>27</v>
@@ -20011,10 +19821,8 @@
       <c r="R97" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S97" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S97" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T97" s="7" t="inlineStr">
         <is>
@@ -20187,10 +19995,10 @@
         <v>21</v>
       </c>
       <c r="J98" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L98" s="6" t="n">
         <v>27</v>
@@ -20202,7 +20010,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P98" s="7" t="n">
         <v>27</v>
@@ -20213,10 +20021,8 @@
       <c r="R98" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S98" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S98" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T98" s="7" t="inlineStr">
         <is>
@@ -20389,10 +20195,10 @@
         <v>21</v>
       </c>
       <c r="J99" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L99" s="6" t="n">
         <v>27</v>
@@ -20404,7 +20210,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P99" s="7" t="n">
         <v>27</v>
@@ -20415,10 +20221,8 @@
       <c r="R99" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S99" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S99" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T99" s="7" t="inlineStr">
         <is>
@@ -20572,9 +20376,9 @@
           <t>220427@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -20591,10 +20395,10 @@
         <v>20</v>
       </c>
       <c r="J100" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L100" s="6" t="n">
         <v>27</v>
@@ -20606,7 +20410,7 @@
         <v>1</v>
       </c>
       <c r="O100" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P100" s="7" t="n">
         <v>27</v>
@@ -20617,10 +20421,8 @@
       <c r="R100" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S100" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S100" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T100" s="7" t="inlineStr">
         <is>
@@ -20793,10 +20595,10 @@
         <v>21</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L101" s="6" t="n">
         <v>27</v>
@@ -20808,7 +20610,7 @@
         <v>0</v>
       </c>
       <c r="O101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P101" s="7" t="n">
         <v>27</v>
@@ -20819,10 +20621,8 @@
       <c r="R101" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S101" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S101" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T101" s="7" t="inlineStr">
         <is>
@@ -20976,9 +20776,9 @@
           <t>220430@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -20995,10 +20795,10 @@
         <v>20</v>
       </c>
       <c r="J102" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K102" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L102" s="6" t="n">
         <v>27</v>
@@ -21010,7 +20810,7 @@
         <v>1</v>
       </c>
       <c r="O102" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P102" s="7" t="n">
         <v>27</v>
@@ -21021,10 +20821,8 @@
       <c r="R102" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S102" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S102" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T102" s="7" t="inlineStr">
         <is>
@@ -21178,9 +20976,9 @@
           <t>220432@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F103" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -21197,10 +20995,10 @@
         <v>20</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K103" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L103" s="6" t="n">
         <v>27</v>
@@ -21212,7 +21010,7 @@
         <v>1</v>
       </c>
       <c r="O103" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P103" s="7" t="n">
         <v>27</v>
@@ -21223,10 +21021,8 @@
       <c r="R103" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S103" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S103" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T103" s="7" t="inlineStr">
         <is>
@@ -21380,9 +21176,9 @@
           <t>220433@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F104" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -21399,10 +21195,10 @@
         <v>20</v>
       </c>
       <c r="J104" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L104" s="6" t="n">
         <v>27</v>
@@ -21414,7 +21210,7 @@
         <v>1</v>
       </c>
       <c r="O104" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P104" s="7" t="n">
         <v>27</v>
@@ -21425,10 +21221,8 @@
       <c r="R104" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S104" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S104" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T104" s="7" t="inlineStr">
         <is>
@@ -21601,10 +21395,10 @@
         <v>21</v>
       </c>
       <c r="J105" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K105" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L105" s="6" t="n">
         <v>27</v>
@@ -21616,7 +21410,7 @@
         <v>0</v>
       </c>
       <c r="O105" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P105" s="7" t="n">
         <v>27</v>
@@ -21627,10 +21421,8 @@
       <c r="R105" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S105" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S105" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T105" s="7" t="inlineStr">
         <is>
@@ -21784,9 +21576,9 @@
           <t>220436@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F106" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -21803,10 +21595,10 @@
         <v>20</v>
       </c>
       <c r="J106" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K106" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L106" s="6" t="n">
         <v>27</v>
@@ -21818,7 +21610,7 @@
         <v>1</v>
       </c>
       <c r="O106" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P106" s="7" t="n">
         <v>27</v>
@@ -21829,10 +21621,8 @@
       <c r="R106" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S106" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S106" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T106" s="7" t="inlineStr">
         <is>
@@ -22005,10 +21795,10 @@
         <v>21</v>
       </c>
       <c r="J107" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L107" s="6" t="n">
         <v>27</v>
@@ -22020,7 +21810,7 @@
         <v>0</v>
       </c>
       <c r="O107" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P107" s="7" t="n">
         <v>27</v>
@@ -22031,10 +21821,8 @@
       <c r="R107" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S107" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S107" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T107" s="7" t="inlineStr">
         <is>
@@ -22207,10 +21995,10 @@
         <v>21</v>
       </c>
       <c r="J108" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L108" s="6" t="n">
         <v>27</v>
@@ -22222,7 +22010,7 @@
         <v>0</v>
       </c>
       <c r="O108" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P108" s="7" t="n">
         <v>27</v>
@@ -22233,10 +22021,8 @@
       <c r="R108" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S108" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S108" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T108" s="7" t="inlineStr">
         <is>
@@ -22390,9 +22176,9 @@
           <t>220439@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F109" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -22409,10 +22195,10 @@
         <v>20</v>
       </c>
       <c r="J109" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K109" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L109" s="6" t="n">
         <v>27</v>
@@ -22424,7 +22210,7 @@
         <v>1</v>
       </c>
       <c r="O109" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" s="7" t="n">
         <v>27</v>
@@ -22435,10 +22221,8 @@
       <c r="R109" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S109" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S109" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T109" s="7" t="inlineStr">
         <is>
@@ -22592,9 +22376,9 @@
           <t>220440@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F110" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -22611,10 +22395,10 @@
         <v>20</v>
       </c>
       <c r="J110" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L110" s="6" t="n">
         <v>27</v>
@@ -22626,7 +22410,7 @@
         <v>1</v>
       </c>
       <c r="O110" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" s="7" t="n">
         <v>27</v>
@@ -22637,10 +22421,8 @@
       <c r="R110" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S110" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S110" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T110" s="7" t="inlineStr">
         <is>
@@ -22813,10 +22595,10 @@
         <v>21</v>
       </c>
       <c r="J111" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K111" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L111" s="6" t="n">
         <v>27</v>
@@ -22828,7 +22610,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P111" s="7" t="n">
         <v>27</v>
@@ -22839,10 +22621,8 @@
       <c r="R111" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S111" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S111" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T111" s="7" t="inlineStr">
         <is>
@@ -22996,9 +22776,9 @@
           <t>220442@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F112" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -23015,10 +22795,10 @@
         <v>20</v>
       </c>
       <c r="J112" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L112" s="6" t="n">
         <v>27</v>
@@ -23030,7 +22810,7 @@
         <v>1</v>
       </c>
       <c r="O112" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P112" s="7" t="n">
         <v>27</v>
@@ -23041,10 +22821,8 @@
       <c r="R112" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S112" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S112" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T112" s="7" t="inlineStr">
         <is>
@@ -23198,9 +22976,9 @@
           <t>220443@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F113" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -23217,10 +22995,10 @@
         <v>20</v>
       </c>
       <c r="J113" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L113" s="6" t="n">
         <v>27</v>
@@ -23232,7 +23010,7 @@
         <v>1</v>
       </c>
       <c r="O113" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P113" s="7" t="n">
         <v>27</v>
@@ -23243,10 +23021,8 @@
       <c r="R113" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S113" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S113" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T113" s="7" t="inlineStr">
         <is>
@@ -23400,9 +23176,9 @@
           <t>220445@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F114" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -23419,10 +23195,10 @@
         <v>20</v>
       </c>
       <c r="J114" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L114" s="6" t="n">
         <v>27</v>
@@ -23434,7 +23210,7 @@
         <v>1</v>
       </c>
       <c r="O114" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P114" s="7" t="n">
         <v>27</v>
@@ -23445,10 +23221,8 @@
       <c r="R114" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S114" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S114" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T114" s="7" t="inlineStr">
         <is>
@@ -23602,9 +23376,9 @@
           <t>220446@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F115" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -23621,10 +23395,10 @@
         <v>20</v>
       </c>
       <c r="J115" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K115" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L115" s="6" t="n">
         <v>27</v>
@@ -23636,7 +23410,7 @@
         <v>1</v>
       </c>
       <c r="O115" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P115" s="7" t="n">
         <v>27</v>
@@ -23647,10 +23421,8 @@
       <c r="R115" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S115" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S115" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T115" s="7" t="inlineStr">
         <is>
@@ -23823,10 +23595,10 @@
         <v>21</v>
       </c>
       <c r="J116" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L116" s="6" t="n">
         <v>27</v>
@@ -23838,7 +23610,7 @@
         <v>0</v>
       </c>
       <c r="O116" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P116" s="7" t="n">
         <v>27</v>
@@ -23849,10 +23621,8 @@
       <c r="R116" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S116" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S116" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T116" s="7" t="inlineStr">
         <is>
@@ -24006,9 +23776,9 @@
           <t>220450@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F117" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -24025,10 +23795,10 @@
         <v>20</v>
       </c>
       <c r="J117" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K117" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L117" s="6" t="n">
         <v>27</v>
@@ -24040,7 +23810,7 @@
         <v>1</v>
       </c>
       <c r="O117" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P117" s="7" t="n">
         <v>27</v>
@@ -24051,10 +23821,8 @@
       <c r="R117" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S117" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S117" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T117" s="7" t="inlineStr">
         <is>
@@ -24208,9 +23976,9 @@
           <t>220451@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F118" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -24227,10 +23995,10 @@
         <v>20</v>
       </c>
       <c r="J118" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L118" s="6" t="n">
         <v>27</v>
@@ -24242,7 +24010,7 @@
         <v>1</v>
       </c>
       <c r="O118" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P118" s="7" t="n">
         <v>27</v>
@@ -24253,10 +24021,8 @@
       <c r="R118" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S118" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S118" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T118" s="7" t="inlineStr">
         <is>
@@ -24410,9 +24176,9 @@
           <t>220453@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F119" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -24429,10 +24195,10 @@
         <v>20</v>
       </c>
       <c r="J119" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K119" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L119" s="6" t="n">
         <v>27</v>
@@ -24444,7 +24210,7 @@
         <v>1</v>
       </c>
       <c r="O119" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P119" s="7" t="n">
         <v>27</v>
@@ -24455,10 +24221,8 @@
       <c r="R119" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S119" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S119" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T119" s="7" t="inlineStr">
         <is>
@@ -24612,9 +24376,9 @@
           <t>220454@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F120" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -24631,10 +24395,10 @@
         <v>20</v>
       </c>
       <c r="J120" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L120" s="6" t="n">
         <v>27</v>
@@ -24646,7 +24410,7 @@
         <v>1</v>
       </c>
       <c r="O120" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P120" s="7" t="n">
         <v>27</v>
@@ -24657,10 +24421,8 @@
       <c r="R120" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S120" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S120" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T120" s="7" t="inlineStr">
         <is>
@@ -24833,10 +24595,10 @@
         <v>21</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K121" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L121" s="6" t="n">
         <v>27</v>
@@ -24848,7 +24610,7 @@
         <v>0</v>
       </c>
       <c r="O121" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P121" s="7" t="n">
         <v>27</v>
@@ -24859,10 +24621,8 @@
       <c r="R121" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S121" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S121" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T121" s="7" t="inlineStr">
         <is>
@@ -25035,10 +24795,10 @@
         <v>21</v>
       </c>
       <c r="J122" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L122" s="6" t="n">
         <v>27</v>
@@ -25050,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="O122" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P122" s="7" t="n">
         <v>27</v>
@@ -25061,10 +24821,8 @@
       <c r="R122" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S122" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S122" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T122" s="7" t="inlineStr">
         <is>
@@ -25237,10 +24995,10 @@
         <v>21</v>
       </c>
       <c r="J123" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K123" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L123" s="6" t="n">
         <v>27</v>
@@ -25252,7 +25010,7 @@
         <v>0</v>
       </c>
       <c r="O123" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P123" s="7" t="n">
         <v>27</v>
@@ -25263,10 +25021,8 @@
       <c r="R123" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S123" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S123" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T123" s="7" t="inlineStr">
         <is>
@@ -25420,9 +25176,9 @@
           <t>220459@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F124" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -25439,10 +25195,10 @@
         <v>20</v>
       </c>
       <c r="J124" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L124" s="6" t="n">
         <v>27</v>
@@ -25454,7 +25210,7 @@
         <v>1</v>
       </c>
       <c r="O124" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P124" s="7" t="n">
         <v>27</v>
@@ -25465,10 +25221,8 @@
       <c r="R124" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S124" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S124" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T124" s="7" t="inlineStr">
         <is>
@@ -25641,10 +25395,10 @@
         <v>21</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K125" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L125" s="6" t="n">
         <v>27</v>
@@ -25656,7 +25410,7 @@
         <v>0</v>
       </c>
       <c r="O125" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P125" s="7" t="n">
         <v>27</v>
@@ -25667,10 +25421,8 @@
       <c r="R125" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S125" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S125" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T125" s="7" t="inlineStr">
         <is>
@@ -25843,10 +25595,10 @@
         <v>21</v>
       </c>
       <c r="J126" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" s="6" t="n">
         <v>27</v>
@@ -25858,7 +25610,7 @@
         <v>0</v>
       </c>
       <c r="O126" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P126" s="7" t="n">
         <v>27</v>
@@ -25869,10 +25621,8 @@
       <c r="R126" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S126" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S126" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T126" s="7" t="inlineStr">
         <is>
@@ -26045,10 +25795,10 @@
         <v>21</v>
       </c>
       <c r="J127" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L127" s="6" t="n">
         <v>27</v>
@@ -26060,7 +25810,7 @@
         <v>0</v>
       </c>
       <c r="O127" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P127" s="7" t="n">
         <v>27</v>
@@ -26071,10 +25821,8 @@
       <c r="R127" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S127" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S127" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T127" s="7" t="inlineStr">
         <is>
@@ -26228,9 +25976,9 @@
           <t>220463@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F128" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -26247,10 +25995,10 @@
         <v>20</v>
       </c>
       <c r="J128" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K128" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L128" s="6" t="n">
         <v>27</v>
@@ -26262,7 +26010,7 @@
         <v>1</v>
       </c>
       <c r="O128" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P128" s="7" t="n">
         <v>27</v>
@@ -26273,10 +26021,8 @@
       <c r="R128" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S128" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S128" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T128" s="7" t="inlineStr">
         <is>
@@ -26430,9 +26176,9 @@
           <t>220464@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F129" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
@@ -26449,10 +26195,10 @@
         <v>20</v>
       </c>
       <c r="J129" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K129" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L129" s="6" t="n">
         <v>27</v>
@@ -26464,7 +26210,7 @@
         <v>1</v>
       </c>
       <c r="O129" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P129" s="7" t="n">
         <v>27</v>
@@ -26475,10 +26221,8 @@
       <c r="R129" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S129" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S129" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T129" s="7" t="inlineStr">
         <is>
@@ -26632,9 +26376,9 @@
           <t>220465@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F130" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -26651,10 +26395,10 @@
         <v>20</v>
       </c>
       <c r="J130" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L130" s="6" t="n">
         <v>27</v>
@@ -26666,7 +26410,7 @@
         <v>1</v>
       </c>
       <c r="O130" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P130" s="7" t="n">
         <v>27</v>
@@ -26677,10 +26421,8 @@
       <c r="R130" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S130" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S130" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T130" s="7" t="inlineStr">
         <is>
@@ -26834,9 +26576,9 @@
           <t>220466@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F131" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -26853,10 +26595,10 @@
         <v>20</v>
       </c>
       <c r="J131" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K131" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L131" s="6" t="n">
         <v>27</v>
@@ -26868,7 +26610,7 @@
         <v>1</v>
       </c>
       <c r="O131" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P131" s="7" t="n">
         <v>27</v>
@@ -26879,10 +26621,8 @@
       <c r="R131" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S131" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S131" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T131" s="7" t="inlineStr">
         <is>
@@ -27055,10 +26795,10 @@
         <v>21</v>
       </c>
       <c r="J132" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K132" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L132" s="6" t="n">
         <v>27</v>
@@ -27070,7 +26810,7 @@
         <v>0</v>
       </c>
       <c r="O132" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P132" s="7" t="n">
         <v>27</v>
@@ -27081,10 +26821,8 @@
       <c r="R132" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S132" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S132" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T132" s="7" t="inlineStr">
         <is>
@@ -27257,10 +26995,10 @@
         <v>21</v>
       </c>
       <c r="J133" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K133" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L133" s="6" t="n">
         <v>27</v>
@@ -27272,7 +27010,7 @@
         <v>0</v>
       </c>
       <c r="O133" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P133" s="7" t="n">
         <v>27</v>
@@ -27283,10 +27021,8 @@
       <c r="R133" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S133" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S133" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T133" s="7" t="inlineStr">
         <is>
@@ -27440,9 +27176,9 @@
           <t>220470@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F134" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -27459,10 +27195,10 @@
         <v>20</v>
       </c>
       <c r="J134" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L134" s="6" t="n">
         <v>27</v>
@@ -27474,7 +27210,7 @@
         <v>1</v>
       </c>
       <c r="O134" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P134" s="7" t="n">
         <v>27</v>
@@ -27485,10 +27221,8 @@
       <c r="R134" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S134" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S134" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T134" s="7" t="inlineStr">
         <is>
@@ -27642,9 +27376,9 @@
           <t>220471@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F135" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
@@ -27661,10 +27395,10 @@
         <v>20</v>
       </c>
       <c r="J135" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K135" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L135" s="6" t="n">
         <v>27</v>
@@ -27676,7 +27410,7 @@
         <v>1</v>
       </c>
       <c r="O135" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P135" s="7" t="n">
         <v>27</v>
@@ -27687,10 +27421,8 @@
       <c r="R135" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S135" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S135" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T135" s="7" t="inlineStr">
         <is>
@@ -27863,10 +27595,10 @@
         <v>21</v>
       </c>
       <c r="J136" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K136" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L136" s="6" t="n">
         <v>27</v>
@@ -27878,7 +27610,7 @@
         <v>0</v>
       </c>
       <c r="O136" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P136" s="7" t="n">
         <v>27</v>
@@ -27889,10 +27621,8 @@
       <c r="R136" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S136" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S136" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T136" s="7" t="inlineStr">
         <is>
@@ -28046,9 +27776,9 @@
           <t>220474@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F137" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
@@ -28065,10 +27795,10 @@
         <v>20</v>
       </c>
       <c r="J137" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K137" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L137" s="6" t="n">
         <v>27</v>
@@ -28080,7 +27810,7 @@
         <v>1</v>
       </c>
       <c r="O137" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P137" s="7" t="n">
         <v>27</v>
@@ -28091,10 +27821,8 @@
       <c r="R137" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S137" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S137" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T137" s="7" t="inlineStr">
         <is>
@@ -28248,9 +27976,9 @@
           <t>220476@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F138" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -28267,10 +27995,10 @@
         <v>20</v>
       </c>
       <c r="J138" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K138" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L138" s="6" t="n">
         <v>27</v>
@@ -28282,7 +28010,7 @@
         <v>1</v>
       </c>
       <c r="O138" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P138" s="7" t="n">
         <v>27</v>
@@ -28293,10 +28021,8 @@
       <c r="R138" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S138" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S138" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T138" s="7" t="inlineStr">
         <is>
@@ -28450,9 +28176,9 @@
           <t>220477@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F139" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
@@ -28469,10 +28195,10 @@
         <v>20</v>
       </c>
       <c r="J139" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L139" s="6" t="n">
         <v>27</v>
@@ -28484,7 +28210,7 @@
         <v>1</v>
       </c>
       <c r="O139" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P139" s="7" t="n">
         <v>27</v>
@@ -28495,10 +28221,8 @@
       <c r="R139" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S139" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S139" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T139" s="7" t="inlineStr">
         <is>
@@ -28671,10 +28395,10 @@
         <v>21</v>
       </c>
       <c r="J140" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K140" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L140" s="6" t="n">
         <v>27</v>
@@ -28686,7 +28410,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P140" s="7" t="n">
         <v>27</v>
@@ -28697,10 +28421,8 @@
       <c r="R140" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S140" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S140" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T140" s="7" t="inlineStr">
         <is>
@@ -28854,9 +28576,9 @@
           <t>220479@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F141" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
@@ -28873,10 +28595,10 @@
         <v>20</v>
       </c>
       <c r="J141" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K141" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L141" s="6" t="n">
         <v>27</v>
@@ -28888,7 +28610,7 @@
         <v>1</v>
       </c>
       <c r="O141" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P141" s="7" t="n">
         <v>27</v>
@@ -28899,10 +28621,8 @@
       <c r="R141" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S141" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S141" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T141" s="7" t="inlineStr">
         <is>
@@ -29056,9 +28776,9 @@
           <t>220480@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F142" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -29075,10 +28795,10 @@
         <v>20</v>
       </c>
       <c r="J142" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K142" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L142" s="6" t="n">
         <v>27</v>
@@ -29090,7 +28810,7 @@
         <v>1</v>
       </c>
       <c r="O142" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P142" s="7" t="n">
         <v>27</v>
@@ -29101,10 +28821,8 @@
       <c r="R142" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S142" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S142" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T142" s="7" t="inlineStr">
         <is>
@@ -29258,9 +28976,9 @@
           <t>220482@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F143" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
@@ -29277,10 +28995,10 @@
         <v>20</v>
       </c>
       <c r="J143" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L143" s="6" t="n">
         <v>27</v>
@@ -29292,7 +29010,7 @@
         <v>1</v>
       </c>
       <c r="O143" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P143" s="7" t="n">
         <v>27</v>
@@ -29303,10 +29021,8 @@
       <c r="R143" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S143" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S143" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T143" s="7" t="inlineStr">
         <is>
@@ -29460,9 +29176,9 @@
           <t>220483@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F144" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F144" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
@@ -29479,10 +29195,10 @@
         <v>20</v>
       </c>
       <c r="J144" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K144" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L144" s="6" t="n">
         <v>27</v>
@@ -29494,7 +29210,7 @@
         <v>1</v>
       </c>
       <c r="O144" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P144" s="7" t="n">
         <v>27</v>
@@ -29505,10 +29221,8 @@
       <c r="R144" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S144" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S144" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T144" s="7" t="inlineStr">
         <is>
@@ -29662,9 +29376,9 @@
           <t>220484@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F145" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F145" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
@@ -29681,10 +29395,10 @@
         <v>20</v>
       </c>
       <c r="J145" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K145" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L145" s="6" t="n">
         <v>27</v>
@@ -29696,7 +29410,7 @@
         <v>1</v>
       </c>
       <c r="O145" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P145" s="7" t="n">
         <v>27</v>
@@ -29707,10 +29421,8 @@
       <c r="R145" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S145" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S145" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T145" s="7" t="inlineStr">
         <is>
@@ -29864,9 +29576,9 @@
           <t>220485@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F146" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F146" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
@@ -29883,10 +29595,10 @@
         <v>20</v>
       </c>
       <c r="J146" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K146" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L146" s="6" t="n">
         <v>27</v>
@@ -29898,7 +29610,7 @@
         <v>1</v>
       </c>
       <c r="O146" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P146" s="7" t="n">
         <v>27</v>
@@ -29909,10 +29621,8 @@
       <c r="R146" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S146" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S146" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T146" s="7" t="inlineStr">
         <is>
@@ -30066,9 +29776,9 @@
           <t>220486@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F147" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F147" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
@@ -30085,10 +29795,10 @@
         <v>20</v>
       </c>
       <c r="J147" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K147" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L147" s="6" t="n">
         <v>27</v>
@@ -30100,7 +29810,7 @@
         <v>1</v>
       </c>
       <c r="O147" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P147" s="7" t="n">
         <v>27</v>
@@ -30111,10 +29821,8 @@
       <c r="R147" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S147" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S147" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T147" s="7" t="inlineStr">
         <is>
@@ -30268,9 +29976,9 @@
           <t>220488@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F148" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
@@ -30287,10 +29995,10 @@
         <v>20</v>
       </c>
       <c r="J148" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K148" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L148" s="6" t="n">
         <v>27</v>
@@ -30302,7 +30010,7 @@
         <v>1</v>
       </c>
       <c r="O148" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P148" s="7" t="n">
         <v>27</v>
@@ -30313,10 +30021,8 @@
       <c r="R148" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S148" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S148" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T148" s="7" t="inlineStr">
         <is>
@@ -30489,10 +30195,10 @@
         <v>21</v>
       </c>
       <c r="J149" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K149" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L149" s="6" t="n">
         <v>27</v>
@@ -30504,7 +30210,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P149" s="7" t="n">
         <v>27</v>
@@ -30515,10 +30221,8 @@
       <c r="R149" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S149" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S149" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T149" s="7" t="inlineStr">
         <is>
@@ -30672,9 +30376,9 @@
           <t>220490@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F150" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
@@ -30691,10 +30395,10 @@
         <v>20</v>
       </c>
       <c r="J150" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K150" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L150" s="6" t="n">
         <v>27</v>
@@ -30706,7 +30410,7 @@
         <v>1</v>
       </c>
       <c r="O150" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P150" s="7" t="n">
         <v>27</v>
@@ -30717,10 +30421,8 @@
       <c r="R150" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S150" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S150" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T150" s="7" t="inlineStr">
         <is>
@@ -30874,9 +30576,9 @@
           <t>220491@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F151" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
@@ -30893,10 +30595,10 @@
         <v>20</v>
       </c>
       <c r="J151" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K151" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L151" s="6" t="n">
         <v>27</v>
@@ -30908,7 +30610,7 @@
         <v>1</v>
       </c>
       <c r="O151" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P151" s="7" t="n">
         <v>27</v>
@@ -30919,10 +30621,8 @@
       <c r="R151" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S151" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S151" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T151" s="7" t="inlineStr">
         <is>
@@ -31076,9 +30776,9 @@
           <t>220492@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F152" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
@@ -31095,10 +30795,10 @@
         <v>20</v>
       </c>
       <c r="J152" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K152" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L152" s="6" t="n">
         <v>27</v>
@@ -31110,7 +30810,7 @@
         <v>1</v>
       </c>
       <c r="O152" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P152" s="7" t="n">
         <v>27</v>
@@ -31121,10 +30821,8 @@
       <c r="R152" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S152" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S152" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T152" s="7" t="inlineStr">
         <is>
@@ -31278,9 +30976,9 @@
           <t>220493@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F153" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
@@ -31297,10 +30995,10 @@
         <v>20</v>
       </c>
       <c r="J153" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K153" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L153" s="6" t="n">
         <v>27</v>
@@ -31312,7 +31010,7 @@
         <v>1</v>
       </c>
       <c r="O153" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P153" s="7" t="n">
         <v>27</v>
@@ -31323,10 +31021,8 @@
       <c r="R153" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S153" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S153" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T153" s="7" t="inlineStr">
         <is>
@@ -31499,10 +31195,10 @@
         <v>21</v>
       </c>
       <c r="J154" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K154" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L154" s="6" t="n">
         <v>27</v>
@@ -31514,7 +31210,7 @@
         <v>0</v>
       </c>
       <c r="O154" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P154" s="7" t="n">
         <v>27</v>
@@ -31525,10 +31221,8 @@
       <c r="R154" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S154" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S154" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T154" s="7" t="inlineStr">
         <is>
@@ -31682,9 +31376,9 @@
           <t>220496@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F155" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
@@ -31701,10 +31395,10 @@
         <v>20</v>
       </c>
       <c r="J155" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K155" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L155" s="6" t="n">
         <v>27</v>
@@ -31716,7 +31410,7 @@
         <v>1</v>
       </c>
       <c r="O155" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P155" s="7" t="n">
         <v>27</v>
@@ -31727,10 +31421,8 @@
       <c r="R155" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S155" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S155" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T155" s="7" t="inlineStr">
         <is>
@@ -31884,9 +31576,9 @@
           <t>220498@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F156" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
@@ -31903,10 +31595,10 @@
         <v>20</v>
       </c>
       <c r="J156" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K156" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L156" s="6" t="n">
         <v>27</v>
@@ -31918,7 +31610,7 @@
         <v>1</v>
       </c>
       <c r="O156" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P156" s="7" t="n">
         <v>27</v>
@@ -31929,10 +31621,8 @@
       <c r="R156" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S156" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S156" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T156" s="7" t="inlineStr">
         <is>
@@ -32086,9 +31776,9 @@
           <t>220499@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F157" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
@@ -32105,10 +31795,10 @@
         <v>20</v>
       </c>
       <c r="J157" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K157" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L157" s="6" t="n">
         <v>27</v>
@@ -32120,7 +31810,7 @@
         <v>1</v>
       </c>
       <c r="O157" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P157" s="7" t="n">
         <v>27</v>
@@ -32131,10 +31821,8 @@
       <c r="R157" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S157" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S157" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T157" s="7" t="inlineStr">
         <is>
@@ -32307,10 +31995,10 @@
         <v>21</v>
       </c>
       <c r="J158" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K158" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L158" s="6" t="n">
         <v>27</v>
@@ -32322,7 +32010,7 @@
         <v>0</v>
       </c>
       <c r="O158" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P158" s="7" t="n">
         <v>27</v>
@@ -32333,10 +32021,8 @@
       <c r="R158" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S158" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S158" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T158" s="7" t="inlineStr">
         <is>
@@ -32509,10 +32195,10 @@
         <v>21</v>
       </c>
       <c r="J159" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K159" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L159" s="6" t="n">
         <v>27</v>
@@ -32524,7 +32210,7 @@
         <v>0</v>
       </c>
       <c r="O159" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P159" s="7" t="n">
         <v>27</v>
@@ -32535,10 +32221,8 @@
       <c r="R159" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S159" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S159" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T159" s="7" t="inlineStr">
         <is>
@@ -32692,9 +32376,9 @@
           <t>220503@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F160" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F160" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
@@ -32711,10 +32395,10 @@
         <v>20</v>
       </c>
       <c r="J160" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K160" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L160" s="6" t="n">
         <v>27</v>
@@ -32726,7 +32410,7 @@
         <v>1</v>
       </c>
       <c r="O160" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P160" s="7" t="n">
         <v>27</v>
@@ -32737,10 +32421,8 @@
       <c r="R160" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S160" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S160" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T160" s="7" t="inlineStr">
         <is>
@@ -32913,10 +32595,10 @@
         <v>21</v>
       </c>
       <c r="J161" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K161" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L161" s="6" t="n">
         <v>27</v>
@@ -32928,7 +32610,7 @@
         <v>0</v>
       </c>
       <c r="O161" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P161" s="7" t="n">
         <v>27</v>
@@ -32939,10 +32621,8 @@
       <c r="R161" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S161" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S161" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T161" s="7" t="inlineStr">
         <is>
@@ -33115,10 +32795,10 @@
         <v>21</v>
       </c>
       <c r="J162" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K162" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L162" s="6" t="n">
         <v>27</v>
@@ -33130,7 +32810,7 @@
         <v>0</v>
       </c>
       <c r="O162" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P162" s="7" t="n">
         <v>27</v>
@@ -33141,10 +32821,8 @@
       <c r="R162" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S162" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S162" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T162" s="7" t="inlineStr">
         <is>
@@ -33298,9 +32976,9 @@
           <t>220506@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F163" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F163" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
@@ -33317,10 +32995,10 @@
         <v>20</v>
       </c>
       <c r="J163" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K163" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L163" s="6" t="n">
         <v>27</v>
@@ -33332,7 +33010,7 @@
         <v>1</v>
       </c>
       <c r="O163" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P163" s="7" t="n">
         <v>27</v>
@@ -33343,10 +33021,8 @@
       <c r="R163" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S163" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S163" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T163" s="7" t="inlineStr">
         <is>
@@ -33519,10 +33195,10 @@
         <v>21</v>
       </c>
       <c r="J164" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K164" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L164" s="6" t="n">
         <v>27</v>
@@ -33534,7 +33210,7 @@
         <v>0</v>
       </c>
       <c r="O164" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P164" s="7" t="n">
         <v>27</v>
@@ -33545,10 +33221,8 @@
       <c r="R164" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S164" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S164" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T164" s="7" t="inlineStr">
         <is>
@@ -33702,9 +33376,9 @@
           <t>220508@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F165" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F165" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
@@ -33721,10 +33395,10 @@
         <v>20</v>
       </c>
       <c r="J165" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K165" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L165" s="6" t="n">
         <v>27</v>
@@ -33736,7 +33410,7 @@
         <v>1</v>
       </c>
       <c r="O165" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P165" s="7" t="n">
         <v>27</v>
@@ -33747,10 +33421,8 @@
       <c r="R165" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S165" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S165" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T165" s="7" t="inlineStr">
         <is>
@@ -33904,9 +33576,9 @@
           <t>220509@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F166" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
@@ -33923,10 +33595,10 @@
         <v>20</v>
       </c>
       <c r="J166" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K166" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L166" s="6" t="n">
         <v>27</v>
@@ -33938,7 +33610,7 @@
         <v>1</v>
       </c>
       <c r="O166" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P166" s="7" t="n">
         <v>27</v>
@@ -33949,10 +33621,8 @@
       <c r="R166" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S166" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S166" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T166" s="7" t="inlineStr">
         <is>
@@ -34106,9 +33776,9 @@
           <t>220511@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F167" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
@@ -34125,10 +33795,10 @@
         <v>20</v>
       </c>
       <c r="J167" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K167" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L167" s="6" t="n">
         <v>27</v>
@@ -34140,7 +33810,7 @@
         <v>1</v>
       </c>
       <c r="O167" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P167" s="7" t="n">
         <v>27</v>
@@ -34151,10 +33821,8 @@
       <c r="R167" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S167" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S167" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T167" s="7" t="inlineStr">
         <is>
@@ -34308,9 +33976,9 @@
           <t>220512@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F168" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
@@ -34327,10 +33995,10 @@
         <v>20</v>
       </c>
       <c r="J168" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K168" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L168" s="6" t="n">
         <v>27</v>
@@ -34342,7 +34010,7 @@
         <v>1</v>
       </c>
       <c r="O168" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P168" s="7" t="n">
         <v>27</v>
@@ -34353,10 +34021,8 @@
       <c r="R168" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S168" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S168" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T168" s="7" t="inlineStr">
         <is>
@@ -34529,10 +34195,10 @@
         <v>21</v>
       </c>
       <c r="J169" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K169" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L169" s="6" t="n">
         <v>27</v>
@@ -34544,7 +34210,7 @@
         <v>0</v>
       </c>
       <c r="O169" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P169" s="7" t="n">
         <v>27</v>
@@ -34555,10 +34221,8 @@
       <c r="R169" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S169" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S169" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T169" s="7" t="inlineStr">
         <is>
@@ -34731,10 +34395,10 @@
         <v>21</v>
       </c>
       <c r="J170" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K170" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L170" s="6" t="n">
         <v>27</v>
@@ -34746,7 +34410,7 @@
         <v>0</v>
       </c>
       <c r="O170" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P170" s="7" t="n">
         <v>27</v>
@@ -34757,10 +34421,8 @@
       <c r="R170" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S170" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S170" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T170" s="7" t="inlineStr">
         <is>
@@ -34914,9 +34576,9 @@
           <t>220517@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F171" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
@@ -34933,10 +34595,10 @@
         <v>20</v>
       </c>
       <c r="J171" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K171" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L171" s="6" t="n">
         <v>27</v>
@@ -34948,7 +34610,7 @@
         <v>1</v>
       </c>
       <c r="O171" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P171" s="7" t="n">
         <v>27</v>
@@ -34959,10 +34621,8 @@
       <c r="R171" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S171" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S171" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T171" s="7" t="inlineStr">
         <is>
@@ -35116,9 +34776,9 @@
           <t>220518@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F172" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -35135,10 +34795,10 @@
         <v>20</v>
       </c>
       <c r="J172" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K172" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L172" s="6" t="n">
         <v>27</v>
@@ -35150,7 +34810,7 @@
         <v>1</v>
       </c>
       <c r="O172" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P172" s="7" t="n">
         <v>27</v>
@@ -35161,10 +34821,8 @@
       <c r="R172" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S172" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S172" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T172" s="7" t="inlineStr">
         <is>
@@ -35318,9 +34976,9 @@
           <t>220519@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F173" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F173" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
@@ -35337,10 +34995,10 @@
         <v>20</v>
       </c>
       <c r="J173" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K173" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L173" s="6" t="n">
         <v>27</v>
@@ -35352,7 +35010,7 @@
         <v>1</v>
       </c>
       <c r="O173" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P173" s="7" t="n">
         <v>27</v>
@@ -35363,10 +35021,8 @@
       <c r="R173" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S173" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S173" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T173" s="7" t="inlineStr">
         <is>
@@ -35520,9 +35176,9 @@
           <t>220520@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F174" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F174" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -35539,10 +35195,10 @@
         <v>20</v>
       </c>
       <c r="J174" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K174" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L174" s="6" t="n">
         <v>27</v>
@@ -35554,7 +35210,7 @@
         <v>1</v>
       </c>
       <c r="O174" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P174" s="7" t="n">
         <v>27</v>
@@ -35565,10 +35221,8 @@
       <c r="R174" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S174" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S174" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T174" s="7" t="inlineStr">
         <is>
@@ -35741,10 +35395,10 @@
         <v>21</v>
       </c>
       <c r="J175" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K175" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L175" s="6" t="n">
         <v>27</v>
@@ -35756,7 +35410,7 @@
         <v>0</v>
       </c>
       <c r="O175" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P175" s="7" t="n">
         <v>27</v>
@@ -35767,10 +35421,8 @@
       <c r="R175" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S175" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S175" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T175" s="7" t="inlineStr">
         <is>
@@ -35924,9 +35576,9 @@
           <t>220522@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F176" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F176" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -35943,10 +35595,10 @@
         <v>20</v>
       </c>
       <c r="J176" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K176" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L176" s="6" t="n">
         <v>27</v>
@@ -35958,7 +35610,7 @@
         <v>1</v>
       </c>
       <c r="O176" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P176" s="7" t="n">
         <v>27</v>
@@ -35969,10 +35621,8 @@
       <c r="R176" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S176" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S176" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T176" s="7" t="inlineStr">
         <is>
@@ -36126,9 +35776,9 @@
           <t>220523@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F177" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F177" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
@@ -36145,10 +35795,10 @@
         <v>20</v>
       </c>
       <c r="J177" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K177" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L177" s="6" t="n">
         <v>27</v>
@@ -36160,7 +35810,7 @@
         <v>1</v>
       </c>
       <c r="O177" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P177" s="7" t="n">
         <v>27</v>
@@ -36171,10 +35821,8 @@
       <c r="R177" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S177" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S177" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T177" s="7" t="inlineStr">
         <is>
@@ -36347,10 +35995,10 @@
         <v>21</v>
       </c>
       <c r="J178" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K178" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L178" s="6" t="n">
         <v>27</v>
@@ -36362,7 +36010,7 @@
         <v>0</v>
       </c>
       <c r="O178" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P178" s="7" t="n">
         <v>27</v>
@@ -36373,10 +36021,8 @@
       <c r="R178" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S178" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S178" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T178" s="7" t="inlineStr">
         <is>
@@ -36549,10 +36195,10 @@
         <v>21</v>
       </c>
       <c r="J179" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K179" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L179" s="6" t="n">
         <v>27</v>
@@ -36564,7 +36210,7 @@
         <v>0</v>
       </c>
       <c r="O179" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P179" s="7" t="n">
         <v>27</v>
@@ -36575,10 +36221,8 @@
       <c r="R179" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S179" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S179" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T179" s="7" t="inlineStr">
         <is>
@@ -36751,10 +36395,10 @@
         <v>21</v>
       </c>
       <c r="J180" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K180" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L180" s="6" t="n">
         <v>27</v>
@@ -36766,7 +36410,7 @@
         <v>0</v>
       </c>
       <c r="O180" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P180" s="7" t="n">
         <v>27</v>
@@ -36777,10 +36421,8 @@
       <c r="R180" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S180" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S180" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T180" s="7" t="inlineStr">
         <is>
@@ -36953,10 +36595,10 @@
         <v>21</v>
       </c>
       <c r="J181" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K181" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L181" s="6" t="n">
         <v>27</v>
@@ -36968,7 +36610,7 @@
         <v>0</v>
       </c>
       <c r="O181" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P181" s="7" t="n">
         <v>27</v>
@@ -36979,10 +36621,8 @@
       <c r="R181" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S181" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S181" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T181" s="7" t="inlineStr">
         <is>
@@ -37136,9 +36776,9 @@
           <t>220528@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F182" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -37155,10 +36795,10 @@
         <v>20</v>
       </c>
       <c r="J182" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K182" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L182" s="6" t="n">
         <v>27</v>
@@ -37170,7 +36810,7 @@
         <v>1</v>
       </c>
       <c r="O182" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P182" s="7" t="n">
         <v>27</v>
@@ -37181,10 +36821,8 @@
       <c r="R182" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S182" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S182" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T182" s="7" t="inlineStr">
         <is>
@@ -37357,10 +36995,10 @@
         <v>21</v>
       </c>
       <c r="J183" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K183" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L183" s="6" t="n">
         <v>27</v>
@@ -37372,7 +37010,7 @@
         <v>0</v>
       </c>
       <c r="O183" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P183" s="7" t="n">
         <v>27</v>
@@ -37383,10 +37021,8 @@
       <c r="R183" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S183" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S183" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T183" s="7" t="inlineStr">
         <is>
@@ -37559,10 +37195,10 @@
         <v>21</v>
       </c>
       <c r="J184" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K184" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L184" s="6" t="n">
         <v>27</v>
@@ -37574,7 +37210,7 @@
         <v>0</v>
       </c>
       <c r="O184" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P184" s="7" t="n">
         <v>27</v>
@@ -37585,10 +37221,8 @@
       <c r="R184" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S184" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S184" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T184" s="7" t="inlineStr">
         <is>
@@ -37761,10 +37395,10 @@
         <v>21</v>
       </c>
       <c r="J185" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K185" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L185" s="6" t="n">
         <v>27</v>
@@ -37776,7 +37410,7 @@
         <v>0</v>
       </c>
       <c r="O185" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P185" s="7" t="n">
         <v>27</v>
@@ -37787,10 +37421,8 @@
       <c r="R185" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S185" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S185" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T185" s="7" t="inlineStr">
         <is>
@@ -37963,10 +37595,10 @@
         <v>21</v>
       </c>
       <c r="J186" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K186" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L186" s="6" t="n">
         <v>27</v>
@@ -37978,7 +37610,7 @@
         <v>0</v>
       </c>
       <c r="O186" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P186" s="7" t="n">
         <v>27</v>
@@ -37989,10 +37621,8 @@
       <c r="R186" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S186" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S186" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T186" s="7" t="inlineStr">
         <is>
@@ -38165,10 +37795,10 @@
         <v>21</v>
       </c>
       <c r="J187" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K187" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L187" s="6" t="n">
         <v>27</v>
@@ -38180,7 +37810,7 @@
         <v>0</v>
       </c>
       <c r="O187" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P187" s="7" t="n">
         <v>27</v>
@@ -38191,10 +37821,8 @@
       <c r="R187" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S187" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S187" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T187" s="7" t="inlineStr">
         <is>
@@ -38348,9 +37976,9 @@
           <t>220535@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F188" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F188" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -38367,10 +37995,10 @@
         <v>20</v>
       </c>
       <c r="J188" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K188" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L188" s="6" t="n">
         <v>27</v>
@@ -38382,7 +38010,7 @@
         <v>1</v>
       </c>
       <c r="O188" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P188" s="7" t="n">
         <v>27</v>
@@ -38393,10 +38021,8 @@
       <c r="R188" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S188" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S188" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T188" s="7" t="inlineStr">
         <is>
@@ -38569,10 +38195,10 @@
         <v>21</v>
       </c>
       <c r="J189" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K189" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L189" s="6" t="n">
         <v>27</v>
@@ -38584,7 +38210,7 @@
         <v>0</v>
       </c>
       <c r="O189" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P189" s="7" t="n">
         <v>27</v>
@@ -38595,10 +38221,8 @@
       <c r="R189" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S189" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S189" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T189" s="7" t="inlineStr">
         <is>
@@ -38752,9 +38376,9 @@
           <t>220538@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F190" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -38771,10 +38395,10 @@
         <v>20</v>
       </c>
       <c r="J190" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K190" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L190" s="6" t="n">
         <v>27</v>
@@ -38786,7 +38410,7 @@
         <v>1</v>
       </c>
       <c r="O190" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P190" s="7" t="n">
         <v>27</v>
@@ -38797,10 +38421,8 @@
       <c r="R190" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S190" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S190" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T190" s="7" t="inlineStr">
         <is>
@@ -38973,10 +38595,10 @@
         <v>21</v>
       </c>
       <c r="J191" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K191" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L191" s="6" t="n">
         <v>27</v>
@@ -38988,7 +38610,7 @@
         <v>0</v>
       </c>
       <c r="O191" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P191" s="7" t="n">
         <v>27</v>
@@ -38999,10 +38621,8 @@
       <c r="R191" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S191" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S191" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T191" s="7" t="inlineStr">
         <is>
@@ -39175,10 +38795,10 @@
         <v>21</v>
       </c>
       <c r="J192" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K192" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L192" s="6" t="n">
         <v>27</v>
@@ -39190,7 +38810,7 @@
         <v>0</v>
       </c>
       <c r="O192" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P192" s="7" t="n">
         <v>27</v>
@@ -39201,10 +38821,8 @@
       <c r="R192" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S192" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S192" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T192" s="7" t="inlineStr">
         <is>
@@ -39358,9 +38976,9 @@
           <t>220543@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F193" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
@@ -39377,10 +38995,10 @@
         <v>20</v>
       </c>
       <c r="J193" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K193" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L193" s="6" t="n">
         <v>27</v>
@@ -39392,7 +39010,7 @@
         <v>1</v>
       </c>
       <c r="O193" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P193" s="7" t="n">
         <v>27</v>
@@ -39403,10 +39021,8 @@
       <c r="R193" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S193" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S193" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T193" s="7" t="inlineStr">
         <is>
@@ -39579,10 +39195,10 @@
         <v>21</v>
       </c>
       <c r="J194" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K194" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L194" s="6" t="n">
         <v>27</v>
@@ -39594,7 +39210,7 @@
         <v>0</v>
       </c>
       <c r="O194" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P194" s="7" t="n">
         <v>27</v>
@@ -39605,10 +39221,8 @@
       <c r="R194" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S194" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S194" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T194" s="7" t="inlineStr">
         <is>
@@ -39762,9 +39376,9 @@
           <t>220546@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F195" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -39781,10 +39395,10 @@
         <v>20</v>
       </c>
       <c r="J195" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K195" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L195" s="6" t="n">
         <v>27</v>
@@ -39796,7 +39410,7 @@
         <v>1</v>
       </c>
       <c r="O195" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P195" s="7" t="n">
         <v>27</v>
@@ -39807,10 +39421,8 @@
       <c r="R195" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S195" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S195" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T195" s="7" t="inlineStr">
         <is>
@@ -39983,10 +39595,10 @@
         <v>21</v>
       </c>
       <c r="J196" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K196" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L196" s="6" t="n">
         <v>27</v>
@@ -39998,7 +39610,7 @@
         <v>0</v>
       </c>
       <c r="O196" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P196" s="7" t="n">
         <v>27</v>
@@ -40009,10 +39621,8 @@
       <c r="R196" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S196" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S196" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T196" s="7" t="inlineStr">
         <is>
@@ -40166,9 +39776,9 @@
           <t>220549@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F197" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F197" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
@@ -40185,10 +39795,10 @@
         <v>20</v>
       </c>
       <c r="J197" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K197" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L197" s="6" t="n">
         <v>27</v>
@@ -40200,7 +39810,7 @@
         <v>1</v>
       </c>
       <c r="O197" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P197" s="7" t="n">
         <v>27</v>
@@ -40211,10 +39821,8 @@
       <c r="R197" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S197" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S197" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T197" s="7" t="inlineStr">
         <is>
@@ -40368,9 +39976,9 @@
           <t>220555@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F198" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
@@ -40387,10 +39995,10 @@
         <v>20</v>
       </c>
       <c r="J198" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K198" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L198" s="6" t="n">
         <v>27</v>
@@ -40402,7 +40010,7 @@
         <v>1</v>
       </c>
       <c r="O198" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P198" s="7" t="n">
         <v>27</v>
@@ -40413,10 +40021,8 @@
       <c r="R198" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S198" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S198" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T198" s="7" t="inlineStr">
         <is>
@@ -40570,9 +40176,9 @@
           <t>220557@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F199" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
@@ -40589,10 +40195,10 @@
         <v>20</v>
       </c>
       <c r="J199" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K199" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L199" s="6" t="n">
         <v>27</v>
@@ -40604,7 +40210,7 @@
         <v>1</v>
       </c>
       <c r="O199" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P199" s="7" t="n">
         <v>27</v>
@@ -40615,10 +40221,8 @@
       <c r="R199" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S199" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S199" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T199" s="7" t="inlineStr">
         <is>
@@ -40772,9 +40376,9 @@
           <t>220558@med.asu.edu.eg</t>
         </is>
       </c>
-      <c r="F200" s="8" t="inlineStr">
-        <is>
-          <t>No Risk</t>
+      <c r="F200" s="4" t="inlineStr">
+        <is>
+          <t>Low Risk</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
@@ -40791,10 +40395,10 @@
         <v>20</v>
       </c>
       <c r="J200" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K200" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L200" s="6" t="n">
         <v>27</v>
@@ -40806,7 +40410,7 @@
         <v>1</v>
       </c>
       <c r="O200" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P200" s="7" t="n">
         <v>27</v>
@@ -40817,10 +40421,8 @@
       <c r="R200" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S200" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S200" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="T200" s="7" t="inlineStr">
         <is>
@@ -40993,10 +40595,10 @@
         <v>21</v>
       </c>
       <c r="J201" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K201" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L201" s="6" t="n">
         <v>27</v>
@@ -41008,7 +40610,7 @@
         <v>0</v>
       </c>
       <c r="O201" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P201" s="7" t="n">
         <v>27</v>
@@ -41019,10 +40621,8 @@
       <c r="R201" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S201" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S201" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T201" s="7" t="inlineStr">
         <is>
@@ -41195,10 +40795,10 @@
         <v>21</v>
       </c>
       <c r="J202" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K202" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L202" s="6" t="n">
         <v>27</v>
@@ -41210,7 +40810,7 @@
         <v>0</v>
       </c>
       <c r="O202" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P202" s="7" t="n">
         <v>27</v>
@@ -41221,10 +40821,8 @@
       <c r="R202" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S202" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S202" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T202" s="7" t="inlineStr">
         <is>
@@ -41397,10 +40995,10 @@
         <v>21</v>
       </c>
       <c r="J203" s="6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K203" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L203" s="6" t="n">
         <v>27</v>
@@ -41412,7 +41010,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P203" s="7" t="n">
         <v>27</v>
@@ -41423,10 +41021,8 @@
       <c r="R203" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S203" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S203" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="T203" s="7" t="inlineStr">
         <is>
